--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/15. 收费小计.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/15. 收费小计.xlsx
@@ -7,14 +7,14 @@
     <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
-    <sheet name="营业收费系统数据资产" sheetId="1" r:id="rId1"/>
+    <sheet name="收费小计数据标准" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="256">
   <si>
     <t>业务属性</t>
   </si>
@@ -214,13 +214,13 @@
     <t>sensitiveLabel</t>
   </si>
   <si>
-    <t>RCM_P_SUTOTAL_ID</t>
+    <t>RCM_PSUBTOTAL_ID</t>
   </si>
   <si>
     <t>收费小计编号</t>
   </si>
   <si>
-    <t>P_SUTOTAL_ID</t>
+    <t>PSUBTOTAL_ID</t>
   </si>
   <si>
     <t>营业收费系统</t>
@@ -235,10 +235,10 @@
     <t>收费信息</t>
   </si>
   <si>
-    <t>收费小计编号主键唯一标识。</t>
-  </si>
-  <si>
-    <t>系统生成，唯一不可重复，非空。</t>
+    <t>收费小计的唯一标识编号</t>
+  </si>
+  <si>
+    <t>非空</t>
   </si>
   <si>
     <t/>
@@ -283,19 +283,16 @@
     <t>一般业务数据</t>
   </si>
   <si>
-    <t>RCM_P_TOTAL_ID</t>
+    <t>RCM_PTOTAL_ID</t>
   </si>
   <si>
     <t>收费汇总编号</t>
   </si>
   <si>
-    <t>P_TOTAL_ID</t>
-  </si>
-  <si>
-    <t>收费汇总编号，默认为0，结账后更新为汇总编号。</t>
-  </si>
-  <si>
-    <t>结账后自动更新为汇总编号，非空。</t>
+    <t>PTOTAL_ID</t>
+  </si>
+  <si>
+    <t>收费汇总编号，默认为0，结账后更新为汇总ID</t>
   </si>
   <si>
     <t>RCM_PST_METHOD</t>
@@ -307,63 +304,57 @@
     <t>PST_METHOD</t>
   </si>
   <si>
-    <t>收费方式的业务编码标识。</t>
-  </si>
-  <si>
-    <t>取值以收费方式字典为准，非空。</t>
-  </si>
-  <si>
-    <t>关联收费方式字典</t>
-  </si>
-  <si>
-    <t>RCM_PST_INPUTT</t>
-  </si>
-  <si>
-    <t>录入标志</t>
-  </si>
-  <si>
-    <t>PST_INPUTT</t>
-  </si>
-  <si>
-    <t>标识该记录是否完成录入，详见收退标志。</t>
-  </si>
-  <si>
-    <t>取值0/1，允许为空。</t>
+    <t>收费方式编码，对应PST_METHOD字典</t>
+  </si>
+  <si>
+    <t>详见对应业务字典</t>
+  </si>
+  <si>
+    <t>RCM_PST_INOUT</t>
+  </si>
+  <si>
+    <t>收退标志</t>
+  </si>
+  <si>
+    <t>PST_INOUT</t>
+  </si>
+  <si>
+    <t>标识收费或退款的业务标志，详见收退标志字典</t>
   </si>
   <si>
     <t>0-未录入，1-已录入</t>
   </si>
   <si>
+    <t>RCM_PST_THIRD_NO</t>
+  </si>
+  <si>
+    <t>第三方机构代码</t>
+  </si>
+  <si>
+    <t>PST_THIRD_NO</t>
+  </si>
+  <si>
+    <t>第三方支付机构的编码标识</t>
+  </si>
+  <si>
+    <t>允许为空</t>
+  </si>
+  <si>
+    <t>VARCHAR2</t>
+  </si>
+  <si>
+    <t>文本</t>
+  </si>
+  <si>
+    <t>支持中文、自由文本</t>
+  </si>
+  <si>
+    <t>第三方机构编码</t>
+  </si>
+  <si>
     <t>否</t>
   </si>
   <si>
-    <t>RCM_PST_THIRD_NO</t>
-  </si>
-  <si>
-    <t>第三方机构代码</t>
-  </si>
-  <si>
-    <t>PST_THIRD_NO</t>
-  </si>
-  <si>
-    <t>第三方机构业务编码标识。</t>
-  </si>
-  <si>
-    <t>记录第三方机构编码，允许为空。</t>
-  </si>
-  <si>
-    <t>VARCHAR2</t>
-  </si>
-  <si>
-    <t>文本</t>
-  </si>
-  <si>
-    <t>支持中文、自由文本</t>
-  </si>
-  <si>
-    <t>第三方机构编码</t>
-  </si>
-  <si>
     <t>RCM_PST_THIRD_BILLNO</t>
   </si>
   <si>
@@ -373,31 +364,40 @@
     <t>PST_THIRD_BILLNO</t>
   </si>
   <si>
-    <t>第三方平台交易流水号。</t>
-  </si>
-  <si>
-    <t>记录第三方交易流水号，允许为空。</t>
+    <t>第三方支付平台的交易流水号</t>
   </si>
   <si>
     <t>第三方交易流水号</t>
   </si>
   <si>
+    <t>RCM_CASHIER</t>
+  </si>
+  <si>
+    <t>收费员</t>
+  </si>
+  <si>
+    <t>CASHIER</t>
+  </si>
+  <si>
+    <t>执行收费操作的人员编号</t>
+  </si>
+  <si>
+    <t>关联收费员主键</t>
+  </si>
+  <si>
     <t>RCM_PW_ID</t>
   </si>
   <si>
-    <t>收费员</t>
+    <t>收费点</t>
   </si>
   <si>
     <t>PW_ID</t>
   </si>
   <si>
-    <t>收费员主键标识。</t>
-  </si>
-  <si>
-    <t>关联收费员信息，非空。</t>
-  </si>
-  <si>
-    <t>关联收费员主键</t>
+    <t>收费业务发生的收费点编号</t>
+  </si>
+  <si>
+    <t>标准日期时间</t>
   </si>
   <si>
     <t>RCM_PST_TIME</t>
@@ -409,10 +409,7 @@
     <t>PST_TIME</t>
   </si>
   <si>
-    <t>收费发生的时间戳。</t>
-  </si>
-  <si>
-    <t>系统自动记录收费时间，非空。</t>
+    <t>收费业务发生的具体时间</t>
   </si>
   <si>
     <t>DATE</t>
@@ -424,7 +421,7 @@
     <t>日期时间格式</t>
   </si>
   <si>
-    <t>标准日期时间</t>
+    <t>标准日期(YYYYMMDD)</t>
   </si>
   <si>
     <t>RCM_PST_DATE</t>
@@ -436,13 +433,10 @@
     <t>PST_DATE</t>
   </si>
   <si>
-    <t>收费发生的业务日期。</t>
-  </si>
-  <si>
-    <t>记录收费业务日期，非空。</t>
-  </si>
-  <si>
-    <t>标准日期(YYYYMMDD)</t>
+    <t>收费业务对应的日期编码</t>
+  </si>
+  <si>
+    <t>YYYYMM账务年月</t>
   </si>
   <si>
     <t>RCM_BILLING_MONTH</t>
@@ -454,13 +448,10 @@
     <t>BILLING_MONTH</t>
   </si>
   <si>
-    <t>交易对应的账务年月。</t>
-  </si>
-  <si>
-    <t>用于账务核算与对账，非空。</t>
-  </si>
-  <si>
-    <t>YYYYMM账务年月</t>
+    <t>交易归属的财务核算年月</t>
+  </si>
+  <si>
+    <t>自由文本</t>
   </si>
   <si>
     <t>RCM_PST_ACTUAL_MONEY</t>
@@ -472,16 +463,13 @@
     <t>PST_ACTUAL_MONEY</t>
   </si>
   <si>
-    <t>实际收到的款项金额。</t>
-  </si>
-  <si>
-    <t>记录实际收款金额，非空。</t>
+    <t>实际收到的总金额</t>
   </si>
   <si>
     <t>元</t>
   </si>
   <si>
-    <t>非负金额(&gt;=0)</t>
+    <t>金额数值</t>
   </si>
   <si>
     <t>RCM_PST_CASH_MONEY</t>
@@ -493,10 +481,7 @@
     <t>PST_CASH_MONEY</t>
   </si>
   <si>
-    <t>以现金方式收取的金额。</t>
-  </si>
-  <si>
-    <t>记录现金收款金额，非空。</t>
+    <t>现金方式收取的金额</t>
   </si>
   <si>
     <t>RCM_PST_CHEQUE_MONEY</t>
@@ -508,10 +493,7 @@
     <t>PST_CHEQUE_MONEY</t>
   </si>
   <si>
-    <t>以支票方式收取的金额。</t>
-  </si>
-  <si>
-    <t>记录支票收款金额，非空。</t>
+    <t>支票方式收取的金额</t>
   </si>
   <si>
     <t>RCM_PST_VOUCHER_MONEY</t>
@@ -523,10 +505,7 @@
     <t>PST_VOUCHER_MONEY</t>
   </si>
   <si>
-    <t>以回执方式收取的金额。</t>
-  </si>
-  <si>
-    <t>记录回执收款金额，非空。</t>
+    <t>回执方式收取的金额</t>
   </si>
   <si>
     <t>RCM_PST_POS_MONEY</t>
@@ -538,10 +517,7 @@
     <t>PST_POS_MONEY</t>
   </si>
   <si>
-    <t>以POS刷卡方式收取的金额。</t>
-  </si>
-  <si>
-    <t>记录POS收款金额，非空。</t>
+    <t>POS刷卡方式收取的金额</t>
   </si>
   <si>
     <t>RCM_PST_PRESTORE_IN_MONEY</t>
@@ -553,10 +529,259 @@
     <t>PST_PRESTORE_IN_MONEY</t>
   </si>
   <si>
-    <t>以预存方式收取的金额。</t>
-  </si>
-  <si>
-    <t>记录预存收款金额，非空。</t>
+    <t>预存账户充值收取的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_PRESTORE_OUT_MONEY</t>
+  </si>
+  <si>
+    <t>预存付款金额</t>
+  </si>
+  <si>
+    <t>PST_PRESTORE_OUT_MONEY</t>
+  </si>
+  <si>
+    <t>使用预存账户支付的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_FEE_MONEY</t>
+  </si>
+  <si>
+    <t>销账金额</t>
+  </si>
+  <si>
+    <t>PST_FEE_MONEY</t>
+  </si>
+  <si>
+    <t>用于核销账单的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_REPETITION_MONEY</t>
+  </si>
+  <si>
+    <t>重笔金额</t>
+  </si>
+  <si>
+    <t>PST_REPETITION_MONEY</t>
+  </si>
+  <si>
+    <t>重复收费对应的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_PUZZLE_MONEY</t>
+  </si>
+  <si>
+    <t>疑难金额</t>
+  </si>
+  <si>
+    <t>PST_PUZZLE_MONEY</t>
+  </si>
+  <si>
+    <t>存在疑问待核实的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_TEMPORARY_MONEY</t>
+  </si>
+  <si>
+    <t>特账金额</t>
+  </si>
+  <si>
+    <t>PST_TEMPORARY_MONEY</t>
+  </si>
+  <si>
+    <t>特殊账务处理的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_LATEFEE_MONEY</t>
+  </si>
+  <si>
+    <t>违约金金额</t>
+  </si>
+  <si>
+    <t>PST_LATEFEE_MONEY</t>
+  </si>
+  <si>
+    <t>收取的违约金金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_BALANCE_MONEY</t>
+  </si>
+  <si>
+    <t>差额金额</t>
+  </si>
+  <si>
+    <t>PST_BALANCE_MONEY</t>
+  </si>
+  <si>
+    <t>账务调整产生的差额金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_DUE_MONEY</t>
+  </si>
+  <si>
+    <t>找零金额</t>
+  </si>
+  <si>
+    <t>PST_DUE_MONEY</t>
+  </si>
+  <si>
+    <t>现金收费时的找零金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_STATE</t>
+  </si>
+  <si>
+    <t>记录状态</t>
+  </si>
+  <si>
+    <t>PST_STATE</t>
+  </si>
+  <si>
+    <t>收费小计记录的业务状态，详见记录状态字典</t>
+  </si>
+  <si>
+    <t>RCM_PCHEQUE_ID</t>
+  </si>
+  <si>
+    <t>凭证表ID</t>
+  </si>
+  <si>
+    <t>PCHEQUE_ID</t>
+  </si>
+  <si>
+    <t>关联的凭证表编号，无凭证时默认为0</t>
+  </si>
+  <si>
+    <t>RCM_PST_F2F_WECHAT_MONEY</t>
+  </si>
+  <si>
+    <t>微信当面付金额</t>
+  </si>
+  <si>
+    <t>PST_F2F_WECHAT_MONEY</t>
+  </si>
+  <si>
+    <t>微信当面付方式收取的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_F2F_ALIPAY_MONEY</t>
+  </si>
+  <si>
+    <t>支付宝当面付金额</t>
+  </si>
+  <si>
+    <t>PST_F2F_ALIPAY_MONEY</t>
+  </si>
+  <si>
+    <t>支付宝当面付方式收取的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_TYPE</t>
+  </si>
+  <si>
+    <t>柜台收费小类型</t>
+  </si>
+  <si>
+    <t>PST_TYPE</t>
+  </si>
+  <si>
+    <t>柜台收费业务的细分类型</t>
+  </si>
+  <si>
+    <t>RCM_PST_PI2_LATEFEE_MONEY</t>
+  </si>
+  <si>
+    <t>污水费违约金金额</t>
+  </si>
+  <si>
+    <t>PST_PI2_LATEFEE_MONEY</t>
+  </si>
+  <si>
+    <t>污水费对应的违约金金额</t>
+  </si>
+  <si>
+    <t>RCM_SUBCOM_CODE</t>
+  </si>
+  <si>
+    <t>站点编码</t>
+  </si>
+  <si>
+    <t>SUBCOM_CODE</t>
+  </si>
+  <si>
+    <t>业务所属的供水站点编码</t>
+  </si>
+  <si>
+    <t>RCM_SUMMONS_NUMBER</t>
+  </si>
+  <si>
+    <t>传票编号</t>
+  </si>
+  <si>
+    <t>SUMMONS_NUMBER</t>
+  </si>
+  <si>
+    <t>财务传票的编号</t>
+  </si>
+  <si>
+    <t>RCM_SUMMONS_USER</t>
+  </si>
+  <si>
+    <t>传票操作人</t>
+  </si>
+  <si>
+    <t>SUMMONS_USER</t>
+  </si>
+  <si>
+    <t>生成传票的操作人员编号</t>
+  </si>
+  <si>
+    <t>RCM_SUMMONS_TIME</t>
+  </si>
+  <si>
+    <t>传票时间</t>
+  </si>
+  <si>
+    <t>SUMMONS_TIME</t>
+  </si>
+  <si>
+    <t>生成传票的时间</t>
+  </si>
+  <si>
+    <t>RCM_PST_IC_MONEY</t>
+  </si>
+  <si>
+    <t>IC卡金额</t>
+  </si>
+  <si>
+    <t>PST_IC_MONEY</t>
+  </si>
+  <si>
+    <t>IC卡方式收取的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_UNDOPRE_MONEY</t>
+  </si>
+  <si>
+    <t>反预存金额</t>
+  </si>
+  <si>
+    <t>PST_UNDOPRE_MONEY</t>
+  </si>
+  <si>
+    <t>撤销预存操作对应的金额</t>
+  </si>
+  <si>
+    <t>RCM_PST_UNDOPRE_NUM</t>
+  </si>
+  <si>
+    <t>反预存笔数</t>
+  </si>
+  <si>
+    <t>PST_UNDOPRE_NUM</t>
+  </si>
+  <si>
+    <t>撤销预存操作的笔数</t>
   </si>
 </sst>
 </file>
@@ -569,7 +794,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -593,6 +818,11 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -971,7 +1201,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -991,6 +1221,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1113,10 +1358,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1125,36 +1370,33 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1164,98 +1406,101 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1267,10 +1512,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1317,6 +1562,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1664,34 +1912,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="17" width="10" customWidth="1"/>
-    <col min="18" max="19" width="9" customWidth="1"/>
-    <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="24" width="10" customWidth="1"/>
-    <col min="25" max="25" width="26" customWidth="1"/>
-    <col min="26" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="10" customWidth="1"/>
-    <col min="30" max="30" width="14" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="20" width="12" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="22" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="20" customWidth="1"/>
+    <col min="27" max="28" width="12" customWidth="1"/>
+    <col min="29" max="29" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:30">
@@ -1922,11 +2169,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:30">
+    <row r="4" ht="33" spans="1:30">
       <c r="A4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -1956,22 +2203,22 @@
       <c r="K4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="6" t="s">
+      <c r="N4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R4" s="5">
@@ -1983,20 +2230,20 @@
       <c r="T4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="Z4" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA4" s="6" t="s">
@@ -2012,11 +2259,11 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" spans="1:30">
+    <row r="5" ht="33" spans="1:30">
       <c r="A5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2038,7 +2285,7 @@
         <v>92</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>75</v>
@@ -2046,22 +2293,22 @@
       <c r="K5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" s="6" t="s">
+      <c r="N5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R5" s="5">
@@ -2073,20 +2320,20 @@
       <c r="T5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="U5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="V5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="W5" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X5" s="6"/>
       <c r="Y5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z5" s="6" t="s">
+      <c r="Z5" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA5" s="6" t="s">
@@ -2102,15 +2349,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:30">
+    <row r="6" ht="33" spans="1:30">
       <c r="A6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>69</v>
@@ -2125,10 +2372,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>75</v>
@@ -2136,22 +2383,22 @@
       <c r="K6" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="6" t="s">
+      <c r="N6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R6" s="5">
@@ -2163,24 +2410,24 @@
       <c r="T6" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="U6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V6" s="6" t="s">
+      <c r="V6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="W6" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X6" s="6"/>
       <c r="Y6" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z6" s="6" t="s">
+      <c r="Z6" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AB6" s="5" t="s">
         <v>86</v>
@@ -2192,15 +2439,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" spans="1:30">
+    <row r="7" ht="33" spans="1:30">
       <c r="A7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>69</v>
@@ -2215,10 +2462,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>75</v>
@@ -2226,22 +2473,22 @@
       <c r="K7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O7" s="6" t="s">
+      <c r="N7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="Q7" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R7" s="5">
@@ -2253,27 +2500,27 @@
       <c r="T7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="U7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="V7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="W7" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X7" s="6"/>
       <c r="Y7" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z7" s="6" t="s">
+      <c r="Z7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AA7" s="6" t="s">
-        <v>105</v>
+      <c r="AA7" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="AC7" s="5" t="s">
         <v>87</v>
@@ -2282,15 +2529,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" spans="1:30">
+    <row r="8" ht="33" spans="1:30">
       <c r="A8" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>69</v>
@@ -2305,10 +2552,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>75</v>
@@ -2316,23 +2563,23 @@
       <c r="K8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="N8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>113</v>
+      <c r="P8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="R8" s="5">
         <v>50</v>
@@ -2343,27 +2590,27 @@
       <c r="T8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="U8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V8" s="6" t="s">
+      <c r="V8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="W8" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X8" s="6"/>
       <c r="Y8" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z8" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>115</v>
+      <c r="Z8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA8" s="22" t="s">
+        <v>111</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AC8" s="5" t="s">
         <v>87</v>
@@ -2372,15 +2619,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" spans="1:30">
+    <row r="9" ht="33" spans="1:30">
       <c r="A9" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>69</v>
@@ -2395,10 +2642,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>75</v>
@@ -2406,23 +2653,23 @@
       <c r="K9" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O9" s="6" t="s">
+      <c r="N9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O9" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>113</v>
+      <c r="P9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="R9" s="5">
         <v>50</v>
@@ -2433,27 +2680,27 @@
       <c r="T9" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="U9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="V9" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="W9" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X9" s="6"/>
       <c r="Y9" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z9" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA9" s="6" t="s">
-        <v>121</v>
+      <c r="Z9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA9" s="22" t="s">
+        <v>117</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AC9" s="5" t="s">
         <v>87</v>
@@ -2462,15 +2709,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="1:30">
+    <row r="10" ht="33" spans="1:30">
       <c r="A10" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>69</v>
@@ -2485,10 +2732,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>75</v>
@@ -2496,22 +2743,22 @@
       <c r="K10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O10" s="6" t="s">
+      <c r="N10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="Q10" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R10" s="5">
@@ -2523,24 +2770,24 @@
       <c r="T10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U10" s="6" t="s">
+      <c r="U10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V10" s="6" t="s">
+      <c r="V10" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W10" s="6" t="s">
+      <c r="W10" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X10" s="6"/>
       <c r="Y10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z10" s="6" t="s">
+      <c r="Z10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AA10" s="6" t="s">
-        <v>127</v>
+      <c r="AA10" s="22" t="s">
+        <v>122</v>
       </c>
       <c r="AB10" s="5" t="s">
         <v>86</v>
@@ -2552,15 +2799,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1" spans="1:30">
+    <row r="11" ht="33" spans="1:30">
       <c r="A11" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>69</v>
@@ -2575,10 +2822,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>75</v>
@@ -2586,51 +2833,51 @@
       <c r="K11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11" s="6" t="s">
+      <c r="N11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P11" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>134</v>
+      <c r="P11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="R11" s="5">
-        <v>7</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>75</v>
+        <v>22</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="6" t="s">
+      <c r="U11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V11" s="6" t="s">
+      <c r="V11" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W11" s="6" t="s">
+      <c r="W11" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X11" s="6"/>
       <c r="Y11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z11" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA11" s="6" t="s">
-        <v>136</v>
+      <c r="Z11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA11" s="22" t="s">
+        <v>127</v>
       </c>
       <c r="AB11" s="5" t="s">
         <v>86</v>
@@ -2642,15 +2889,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:30">
+    <row r="12" ht="33" spans="1:30">
       <c r="A12" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>138</v>
+        <v>128</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>69</v>
@@ -2665,10 +2912,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>75</v>
@@ -2676,51 +2923,51 @@
       <c r="K12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O12" s="6" t="s">
+      <c r="N12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>79</v>
+      <c r="P12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="R12" s="5">
-        <v>22</v>
-      </c>
-      <c r="S12" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="U12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V12" s="6" t="s">
+      <c r="V12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W12" s="6" t="s">
+      <c r="W12" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X12" s="6"/>
       <c r="Y12" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA12" s="6" t="s">
-        <v>142</v>
+      <c r="Z12" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA12" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="AB12" s="5" t="s">
         <v>86</v>
@@ -2732,15 +2979,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1" spans="1:30">
+    <row r="13" ht="33" spans="1:30">
       <c r="A13" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>144</v>
+        <v>136</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>69</v>
@@ -2755,10 +3002,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>75</v>
@@ -2766,22 +3013,22 @@
       <c r="K13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O13" s="6" t="s">
+      <c r="N13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O13" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="P13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="Q13" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R13" s="5">
@@ -2793,24 +3040,24 @@
       <c r="T13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="U13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V13" s="6" t="s">
+      <c r="V13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W13" s="6" t="s">
+      <c r="W13" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X13" s="6"/>
       <c r="Y13" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z13" s="6" t="s">
+      <c r="Z13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AA13" s="6" t="s">
-        <v>148</v>
+      <c r="AA13" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="AB13" s="5" t="s">
         <v>86</v>
@@ -2822,15 +3069,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1" spans="1:30">
+    <row r="14" ht="33" spans="1:30">
       <c r="A14" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>150</v>
+        <v>141</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>69</v>
@@ -2845,10 +3092,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>75</v>
@@ -2856,51 +3103,51 @@
       <c r="K14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O14" s="6" t="s">
+      <c r="N14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="Q14" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R14" s="5">
         <v>22</v>
       </c>
       <c r="S14" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="U14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="U14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V14" s="6" t="s">
+      <c r="V14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W14" s="6" t="s">
+      <c r="W14" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X14" s="6"/>
       <c r="Y14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z14" s="6" t="s">
+      <c r="Z14" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="AB14" s="5" t="s">
         <v>86</v>
@@ -2912,15 +3159,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1" spans="1:30">
+    <row r="15" ht="33" spans="1:30">
       <c r="A15" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>157</v>
+        <v>146</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>69</v>
@@ -2935,10 +3182,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>75</v>
@@ -2946,22 +3193,22 @@
       <c r="K15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O15" s="6" t="s">
+      <c r="N15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="Q15" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R15" s="5">
@@ -2971,26 +3218,26 @@
         <v>2</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="U15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V15" s="6" t="s">
+      <c r="V15" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="W15" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X15" s="6"/>
       <c r="Y15" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z15" s="6" t="s">
+      <c r="Z15" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA15" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AB15" s="5" t="s">
         <v>86</v>
@@ -3002,15 +3249,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1" spans="1:30">
+    <row r="16" ht="33" spans="1:30">
       <c r="A16" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>162</v>
+        <v>152</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>69</v>
@@ -3025,10 +3272,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>75</v>
@@ -3036,22 +3283,22 @@
       <c r="K16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N16" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O16" s="6" t="s">
+      <c r="N16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="Q16" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R16" s="5">
@@ -3061,26 +3308,26 @@
         <v>2</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="U16" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V16" s="6" t="s">
+      <c r="V16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W16" s="6" t="s">
+      <c r="W16" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X16" s="6"/>
       <c r="Y16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z16" s="6" t="s">
+      <c r="Z16" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AB16" s="5" t="s">
         <v>86</v>
@@ -3092,15 +3339,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" ht="34" customHeight="1" spans="1:30">
+    <row r="17" ht="33" spans="1:30">
       <c r="A17" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>167</v>
+        <v>156</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>69</v>
@@ -3115,10 +3362,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>75</v>
@@ -3126,22 +3373,22 @@
       <c r="K17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O17" s="6" t="s">
+      <c r="N17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="Q17" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R17" s="5">
@@ -3151,26 +3398,26 @@
         <v>2</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="U17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V17" s="6" t="s">
+      <c r="V17" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W17" s="6" t="s">
+      <c r="W17" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X17" s="6"/>
       <c r="Y17" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z17" s="6" t="s">
+      <c r="Z17" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA17" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AB17" s="5" t="s">
         <v>86</v>
@@ -3182,15 +3429,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1" spans="1:30">
+    <row r="18" ht="33" spans="1:30">
       <c r="A18" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>172</v>
+        <v>160</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>69</v>
@@ -3205,10 +3452,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>75</v>
@@ -3216,22 +3463,22 @@
       <c r="K18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N18" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O18" s="6" t="s">
+      <c r="N18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="P18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="Q18" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R18" s="5">
@@ -3241,26 +3488,26 @@
         <v>2</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="U18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V18" s="6" t="s">
+      <c r="V18" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W18" s="6" t="s">
+      <c r="W18" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z18" s="6" t="s">
+      <c r="Z18" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AB18" s="5" t="s">
         <v>86</v>
@@ -3272,15 +3519,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1" spans="1:30">
+    <row r="19" ht="33" spans="1:30">
       <c r="A19" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>177</v>
+        <v>164</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>69</v>
@@ -3295,10 +3542,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>75</v>
@@ -3306,22 +3553,22 @@
       <c r="K19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N19" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O19" s="6" t="s">
+      <c r="N19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="Q19" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R19" s="5">
@@ -3331,26 +3578,26 @@
         <v>2</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="U19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V19" s="6" t="s">
+      <c r="V19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="W19" s="6" t="s">
+      <c r="W19" s="5" t="s">
         <v>82</v>
       </c>
       <c r="X19" s="6"/>
       <c r="Y19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Z19" s="6" t="s">
+      <c r="Z19" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AB19" s="5" t="s">
         <v>86</v>
@@ -3359,6 +3606,1986 @@
         <v>87</v>
       </c>
       <c r="AD19" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" ht="33" spans="1:30">
+      <c r="A20" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R20" s="5">
+        <v>22</v>
+      </c>
+      <c r="S20" s="5">
+        <v>2</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC20" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD20" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" ht="33" spans="1:30">
+      <c r="A21" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R21" s="5">
+        <v>22</v>
+      </c>
+      <c r="S21" s="5">
+        <v>2</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA21" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD21" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" ht="33" spans="1:30">
+      <c r="A22" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R22" s="5">
+        <v>22</v>
+      </c>
+      <c r="S22" s="5">
+        <v>2</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA22" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD22" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" ht="33" spans="1:30">
+      <c r="A23" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R23" s="5">
+        <v>22</v>
+      </c>
+      <c r="S23" s="5">
+        <v>2</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA23" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD23" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" ht="33" spans="1:30">
+      <c r="A24" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R24" s="5">
+        <v>22</v>
+      </c>
+      <c r="S24" s="5">
+        <v>2</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA24" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC24" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD24" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" ht="33" spans="1:30">
+      <c r="A25" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R25" s="5">
+        <v>22</v>
+      </c>
+      <c r="S25" s="5">
+        <v>2</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z25" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA25" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC25" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD25" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" ht="33" spans="1:30">
+      <c r="A26" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R26" s="5">
+        <v>22</v>
+      </c>
+      <c r="S26" s="5">
+        <v>2</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA26" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD26" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" ht="33" spans="1:30">
+      <c r="A27" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R27" s="5">
+        <v>22</v>
+      </c>
+      <c r="S27" s="5">
+        <v>2</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z27" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA27" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD27" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" ht="33" spans="1:30">
+      <c r="A28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R28" s="5">
+        <v>22</v>
+      </c>
+      <c r="S28" s="5">
+        <v>2</v>
+      </c>
+      <c r="T28" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA28" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD28" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" ht="33" spans="1:30">
+      <c r="A29" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R29" s="5">
+        <v>22</v>
+      </c>
+      <c r="S29" s="5">
+        <v>0</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U29" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD29" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" ht="33" spans="1:30">
+      <c r="A30" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R30" s="5">
+        <v>22</v>
+      </c>
+      <c r="S30" s="5">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V30" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z30" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA30" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD30" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" ht="33" spans="1:30">
+      <c r="A31" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R31" s="5">
+        <v>22</v>
+      </c>
+      <c r="S31" s="5">
+        <v>2</v>
+      </c>
+      <c r="T31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U31" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z31" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA31" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD31" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" ht="33" spans="1:30">
+      <c r="A32" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R32" s="5">
+        <v>22</v>
+      </c>
+      <c r="S32" s="5">
+        <v>2</v>
+      </c>
+      <c r="T32" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U32" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z32" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA32" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC32" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD32" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" ht="33" spans="1:30">
+      <c r="A33" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R33" s="5">
+        <v>22</v>
+      </c>
+      <c r="S33" s="5">
+        <v>0</v>
+      </c>
+      <c r="T33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U33" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z33" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA33" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB33" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD33" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" ht="33" spans="1:30">
+      <c r="A34" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R34" s="5">
+        <v>22</v>
+      </c>
+      <c r="S34" s="5">
+        <v>2</v>
+      </c>
+      <c r="T34" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U34" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z34" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA34" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD34" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" ht="33" spans="1:30">
+      <c r="A35" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="R35" s="5">
+        <v>10</v>
+      </c>
+      <c r="S35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="T35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X35" s="6"/>
+      <c r="Y35" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB35" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC35" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD35" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" ht="33" spans="1:30">
+      <c r="A36" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="R36" s="5">
+        <v>50</v>
+      </c>
+      <c r="S36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="T36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U36" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V36" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z36" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA36" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB36" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD36" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" ht="33" spans="1:30">
+      <c r="A37" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R37" s="5">
+        <v>22</v>
+      </c>
+      <c r="S37" s="5">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U37" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z37" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA37" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB37" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD37" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" ht="33" spans="1:30">
+      <c r="A38" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="R38" s="5">
+        <v>7</v>
+      </c>
+      <c r="S38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="T38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W38" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X38" s="6"/>
+      <c r="Y38" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z38" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB38" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC38" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD38" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" ht="33" spans="1:30">
+      <c r="A39" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R39" s="5">
+        <v>22</v>
+      </c>
+      <c r="S39" s="5">
+        <v>4</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V39" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA39" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB39" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC39" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD39" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" ht="33" spans="1:30">
+      <c r="A40" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R40" s="5">
+        <v>22</v>
+      </c>
+      <c r="S40" s="5">
+        <v>4</v>
+      </c>
+      <c r="T40" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U40" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V40" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X40" s="6"/>
+      <c r="Y40" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z40" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA40" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB40" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC40" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD40" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" ht="33" spans="1:30">
+      <c r="A41" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R41" s="5">
+        <v>22</v>
+      </c>
+      <c r="S41" s="5">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V41" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z41" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA41" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB41" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC41" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD41" s="5" t="s">
         <v>88</v>
       </c>
     </row>
